--- a/data/Ocorrencia de acidentes.xlsx
+++ b/data/Ocorrencia de acidentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06C066-5F9D-4B84-8470-AA434F09C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCD6AF0-124B-4D86-8C6B-77F5425A7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="77">
   <si>
     <t>Região</t>
   </si>
@@ -246,6 +246,27 @@
   </si>
   <si>
     <t>10001456970</t>
+  </si>
+  <si>
+    <t>LUCAS EMANUEL TEIXEIRA LEIRIA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>12440481947</t>
+  </si>
+  <si>
+    <t>Conferente</t>
+  </si>
+  <si>
+    <t>GABRIEL DOS SANTOS SOUZA</t>
+  </si>
+  <si>
+    <t>09966551905</t>
+  </si>
+  <si>
+    <t>MARCELO MACIEL DA SILVA</t>
+  </si>
+  <si>
+    <t>46369940860</t>
   </si>
 </sst>
 </file>
@@ -599,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4498545-4542-48C8-A893-C1488B696ACF}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
@@ -1888,6 +1909,129 @@
         <v>27</v>
       </c>
     </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32">
+        <v>46067.5</v>
+      </c>
+      <c r="K32">
+        <v>46067.5</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33">
+        <v>46069.541666666701</v>
+      </c>
+      <c r="K33">
+        <v>46069.541666666701</v>
+      </c>
+      <c r="L33" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34">
+        <v>46079.743055555598</v>
+      </c>
+      <c r="K34">
+        <v>46079.743055555598</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Ocorrencia de acidentes.xlsx
+++ b/data/Ocorrencia de acidentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCD6AF0-124B-4D86-8C6B-77F5425A7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D417D758-0E0C-45ED-92DA-BC0E708C1C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -621,24 +621,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4498545-4542-48C8-A893-C1488B696ACF}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -761,7 +761,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -802,7 +802,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -843,7 +843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -884,7 +884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -925,7 +925,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -966,7 +966,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>

--- a/data/Ocorrencia de acidentes.xlsx
+++ b/data/Ocorrencia de acidentes.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D417D758-0E0C-45ED-92DA-BC0E708C1C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B44210-7A53-4F19-B911-92BB3601D0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$M$34</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -632,7 +635,7 @@
     <col min="7" max="7" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -666,7 +669,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1937,7 +1940,7 @@
       <c r="I32" t="s">
         <v>20</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>46067.5</v>
       </c>
       <c r="K32">
@@ -1978,7 +1981,7 @@
       <c r="I33" t="s">
         <v>20</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>46069.541666666701</v>
       </c>
       <c r="K33">
@@ -2019,7 +2022,7 @@
       <c r="I34" t="s">
         <v>20</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>46079.743055555598</v>
       </c>
       <c r="K34">
@@ -2033,6 +2036,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M34" xr:uid="{E4498545-4542-48C8-A893-C1488B696ACF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Ocorrencia de acidentes.xlsx
+++ b/data/Ocorrencia de acidentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B44210-7A53-4F19-B911-92BB3601D0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B5093-BD38-474D-8D9F-57DA20A5BC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -624,24 +624,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4498545-4542-48C8-A893-C1488B696ACF}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -764,7 +764,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -805,7 +805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -887,7 +887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -969,7 +969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>

--- a/data/Ocorrencia de acidentes.xlsx
+++ b/data/Ocorrencia de acidentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B5093-BD38-474D-8D9F-57DA20A5BC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A33162-F72B-4517-82F4-C0117895B0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12CE4CCA-D515-4483-A606-ADAC2E5F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -624,24 +624,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4498545-4542-48C8-A893-C1488B696ACF}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -764,7 +764,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -805,7 +805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -887,7 +887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -969,7 +969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
